--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OREGON_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/OREGON_2018.xlsx
@@ -391,7 +391,7 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="3">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="D164">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="165">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C207">
@@ -4171,7 +4171,7 @@
         <v>8</v>
       </c>
       <c r="D212">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="213">
@@ -4603,7 +4603,7 @@
         <v>8</v>
       </c>
       <c r="D236">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="237">
@@ -5071,7 +5071,7 @@
         <v>8</v>
       </c>
       <c r="D262">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="263">
@@ -5485,7 +5485,7 @@
         <v>88</v>
       </c>
       <c r="D285">
-        <v>0.009952499434517077</v>
+        <v>0.009952499434517075</v>
       </c>
     </row>
     <row r="286">
@@ -6205,7 +6205,7 @@
         <v>8</v>
       </c>
       <c r="D325">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="326">
@@ -7033,7 +7033,7 @@
         <v>8</v>
       </c>
       <c r="D371">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="372">
@@ -8167,7 +8167,7 @@
         <v>8</v>
       </c>
       <c r="D434">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="435">
@@ -8239,7 +8239,7 @@
         <v>8</v>
       </c>
       <c r="D438">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="439">
@@ -9121,7 +9121,7 @@
         <v>8</v>
       </c>
       <c r="D487">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="488">
@@ -9193,7 +9193,7 @@
         <v>8</v>
       </c>
       <c r="D491">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="492">
@@ -9589,7 +9589,7 @@
         <v>8</v>
       </c>
       <c r="D513">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="514">
@@ -10363,7 +10363,7 @@
         <v>8</v>
       </c>
       <c r="D556">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="557">
@@ -10741,7 +10741,7 @@
         <v>8</v>
       </c>
       <c r="D577">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="578">
@@ -10921,7 +10921,7 @@
         <v>8</v>
       </c>
       <c r="D587">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="588">
@@ -10939,7 +10939,7 @@
         <v>8</v>
       </c>
       <c r="D588">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="589">
@@ -11875,7 +11875,7 @@
         <v>8</v>
       </c>
       <c r="D640">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="641">
@@ -12091,7 +12091,7 @@
         <v>84</v>
       </c>
       <c r="D652">
-        <v>0.009500113096584483</v>
+        <v>0.009500113096584484</v>
       </c>
     </row>
     <row r="653">
@@ -12145,7 +12145,7 @@
         <v>8</v>
       </c>
       <c r="D655">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="656">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C712">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C713">
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="D723">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="724">
@@ -13819,7 +13819,7 @@
         <v>8</v>
       </c>
       <c r="D748">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="749">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C753">
@@ -14719,7 +14719,7 @@
         <v>8</v>
       </c>
       <c r="D798">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="799">
@@ -15655,7 +15655,7 @@
         <v>8</v>
       </c>
       <c r="D850">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="851">
@@ -16519,7 +16519,7 @@
         <v>8</v>
       </c>
       <c r="D898">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="899">
@@ -19777,7 +19777,7 @@
         <v>8</v>
       </c>
       <c r="D1079">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1080">
@@ -19849,7 +19849,7 @@
         <v>8</v>
       </c>
       <c r="D1083">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1084">
@@ -20317,7 +20317,7 @@
         <v>8</v>
       </c>
       <c r="D1109">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1110">
@@ -21505,7 +21505,7 @@
         <v>8</v>
       </c>
       <c r="D1175">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1176">
@@ -21541,7 +21541,7 @@
         <v>8</v>
       </c>
       <c r="D1177">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1178">
@@ -21739,7 +21739,7 @@
         <v>8</v>
       </c>
       <c r="D1188">
-        <v>0.0009047726758651889</v>
+        <v>0.0009047726758651888</v>
       </c>
     </row>
     <row r="1189">
